--- a/administrative_forms/014_project_management_tracker--administrative_forms.xlsx
+++ b/administrative_forms/014_project_management_tracker--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_1</t>
+          <t>project_title_page</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Project Management Tracker Page 1</t>
+          <t>Project Title</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_2</t>
+          <t>task_list_page</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_3</t>
+          <t>deadline_page</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_4</t>
+          <t>resources_page</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Resource Management</t>
+          <t>Resources</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_5</t>
+          <t>task_status_page</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Task Status</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,24 +630,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_6</t>
+          <t>project_description_page</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Task Deadline</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Deadline is a date in the format YYYY-MM-DD</t>
-        </is>
-      </c>
+          <t>Project Description</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -657,24 +653,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_7</t>
+          <t>task_description_page</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Task Time</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Time in the format HH:MM</t>
-        </is>
-      </c>
+          <t>Task Description</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -684,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_8</t>
+          <t>project_deadline_page</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Task Status</t>
+          <t>Project Deadline</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -707,24 +699,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_9</t>
+          <t>project_time_page</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Task Description</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Description of the task</t>
-        </is>
-      </c>
+          <t>Project Time</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -734,24 +722,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_10</t>
+          <t>project_status_page</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Project Description</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Description of the project</t>
-        </is>
-      </c>
+          <t>Project Status</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -761,24 +745,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_11</t>
+          <t>task_time_page</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Project Deadline</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Project deadline is a date in the format YYYY-MM-DD</t>
-        </is>
-      </c>
+          <t>Task Time</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -788,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_12</t>
+          <t>task_priority_page</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Project Resources</t>
+          <t>Task Priority</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -811,24 +791,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_13</t>
+          <t>task_resources_page</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Project Time</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Project time in the format HH:MM</t>
-        </is>
-      </c>
+          <t>Task Resources</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -838,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_14</t>
+          <t>project_resources_page</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Project Status</t>
+          <t>Project Resources</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -866,7 +842,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_15</t>
+          <t>project_priority_page</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -889,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_16</t>
+          <t>task_priority_page_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Task Priority</t>
+          <t>Task Priority Page 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -907,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_17</t>
+          <t>project_time_page_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Task Resources</t>
+          <t>Project Time Page 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -930,186 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_18</t>
+          <t>project_description_page_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Project Resources</t>
+          <t>Project Description Page 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>project_management_tracker_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Project Priority</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>project_management_tracker_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Task Priority</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>project_management_tracker_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Project Time</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Project time in the format HH:MM</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>project_management_tracker_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Project Status</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>project_management_tracker_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Task Status</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>project_management_tracker_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Project Description</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>project_management_tracker_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Task Description</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1126,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1154,7 +965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_2_choices</t>
+          <t>task_list_page_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1171,7 +982,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_2_choices</t>
+          <t>task_list_page_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1188,7 +999,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_2_choices</t>
+          <t>task_list_page_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1205,391 +1016,255 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_5_choices</t>
+          <t>resources_page_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>resource_a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>Resource A</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_5_choices</t>
+          <t>resources_page_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>other_option</t>
+          <t>resource_b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>other option</t>
+          <t>Resource B</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_8_choices</t>
+          <t>resources_page_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>resource_c</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resource C</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_8_choices</t>
+          <t>task_status_page_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_8_choices</t>
+          <t>task_status_page_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_12_choices</t>
+          <t>task_status_page_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>resource_a</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Resource A</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_12_choices</t>
+          <t>project_status_page_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>resource_b</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Resource B</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_12_choices</t>
+          <t>project_status_page_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>resource_c</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Resource C</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_14_choices</t>
+          <t>project_status_page_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_14_choices</t>
+          <t>task_resources_page_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>resource_a</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Resource A</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_14_choices</t>
+          <t>task_resources_page_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>resource_b</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Resource B</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_17_choices</t>
+          <t>task_resources_page_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>resource_a</t>
+          <t>resource_c</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Resource A</t>
+          <t>Resource C</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_17_choices</t>
+          <t>project_resources_page_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>resource_b</t>
+          <t>resource_a</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Resource B</t>
+          <t>Resource A</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_17_choices</t>
+          <t>project_resources_page_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>resource_c</t>
+          <t>resource_b</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Resource C</t>
+          <t>Resource B</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>project_management_tracker_page_18_choices</t>
+          <t>project_resources_page_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>resource_a</t>
+          <t>resource_c</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Resource A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>project_management_tracker_page_18_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>resource_b</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Resource B</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>project_management_tracker_page_18_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>resource_c</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
           <t>Resource C</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>project_management_tracker_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>project_management_tracker_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>project_management_tracker_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>project_management_tracker_page_23_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>project_management_tracker_page_23_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>project_management_tracker_page_23_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Completed</t>
         </is>
       </c>
     </row>
